--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2489-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2489-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E505630-2E32-4B5B-80D2-19DF1AC57D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03C9DE2C-6FF2-49D8-977B-FAC58EE06CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{901C8B7F-814C-4B83-82C0-CF98EEB0F4CE}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{D956D9CF-2DF3-452D-93DB-6285CA7B9AE0}"/>
   </bookViews>
   <sheets>
     <sheet name="2489-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1481,21 +1481,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385E6A60-2E8B-48A9-9F76-71BC98FB5CD0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE00C2B9-31F3-44F0-981E-16DF76A59DFB}">
   <dimension ref="A1:R49"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" customWidth="1"/>
-    <col min="4" max="10" width="8.21875" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.21875" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1523,7 +1523,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1553,7 +1553,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1649,7 +1649,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2026</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>2025</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="38">
         <v>2024</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="40">
         <v>2023</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>26</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="38">
         <v>2022</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="40">
         <v>2021</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>2020</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="40">
         <v>2019</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>26</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>26</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="38">
         <v>2018</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="40">
         <v>2017</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="38">
         <v>2016</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>7.83</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="40">
         <v>2015</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>9.33</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="38">
         <v>2014</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="40">
         <v>2013</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>9.9700000000000006</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="38">
         <v>2012</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>8.52</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="40">
         <v>2011</v>
       </c>
@@ -3353,7 +3353,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="38">
         <v>2010</v>
       </c>
@@ -3407,7 +3407,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="40">
         <v>2009</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="38">
         <v>2008</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="40">
         <v>2007</v>
       </c>
@@ -3569,7 +3569,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="38">
         <v>2006</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="40">
         <v>2005</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>6.44</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="38">
         <v>2004</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="40">
         <v>2003</v>
       </c>
@@ -3785,7 +3785,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="38">
         <v>2002</v>
       </c>
@@ -3839,7 +3839,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="40">
         <v>2001</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>6.48</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="38">
         <v>2000</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="40">
         <v>1999</v>
       </c>
@@ -4001,7 +4001,7 @@
         <v>8.1300000000000008</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="38">
         <v>1998</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="40" t="s">
         <v>45</v>
       </c>
